--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92541646932</v>
+        <v>46157.93116709341</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116709341</v>
+        <v>46157.93369504009</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93369504009</v>
+        <v>46157.93673823427</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93673823427</v>
+        <v>46158.28195497847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28195497847</v>
+        <v>46158.29719776291</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29719776291</v>
+        <v>46158.29792127723</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29792127723</v>
+        <v>46158.33356949694</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33356949694</v>
+        <v>46158.37211482676</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211482676</v>
+        <v>46158.37268423541</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
